--- a/Daftar_Saham_KOMPAS100.xlsx
+++ b/Daftar_Saham_KOMPAS100.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex.kelana/Desktop/IDX/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex.kelana/Desktop/IDX/Deploy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCCFDA7-5912-CE4A-817B-1D94319FD919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D9477A-FC70-6B46-815C-1B9E406305AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4720" yWindow="860" windowWidth="28880" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11920" yWindow="2180" windowWidth="28880" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lampiran 4" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="116">
   <si>
     <t>No.</t>
   </si>
@@ -47,15 +47,9 @@
     <t>Kode</t>
   </si>
   <si>
-    <t>AADI</t>
-  </si>
-  <si>
     <t>ACES</t>
   </si>
   <si>
-    <t>ADMR</t>
-  </si>
-  <si>
     <t>ADRO</t>
   </si>
   <si>
@@ -71,9 +65,6 @@
     <t>ANTM</t>
   </si>
   <si>
-    <t>ARCI</t>
-  </si>
-  <si>
     <t>ARTO</t>
   </si>
   <si>
@@ -92,42 +83,21 @@
     <t>BBTN</t>
   </si>
   <si>
-    <t>BBYB</t>
-  </si>
-  <si>
-    <t>BKSL</t>
-  </si>
-  <si>
     <t>BMRI</t>
   </si>
   <si>
     <t>BRIS</t>
   </si>
   <si>
-    <t>BRMS</t>
-  </si>
-  <si>
     <t>BRPT</t>
   </si>
   <si>
     <t>BSDE</t>
   </si>
   <si>
-    <t>BUKA</t>
-  </si>
-  <si>
-    <t>BULL</t>
-  </si>
-  <si>
     <t>BUMI</t>
   </si>
   <si>
-    <t>BUVA</t>
-  </si>
-  <si>
-    <t>CBDK</t>
-  </si>
-  <si>
     <t>CMRY</t>
   </si>
   <si>
@@ -137,12 +107,6 @@
     <t>CTRA</t>
   </si>
   <si>
-    <t>CUAN</t>
-  </si>
-  <si>
-    <t>DEWA</t>
-  </si>
-  <si>
     <t>DSNG</t>
   </si>
   <si>
@@ -158,9 +122,6 @@
     <t>ERAA</t>
   </si>
   <si>
-    <t>ESSA</t>
-  </si>
-  <si>
     <t>EXCL</t>
   </si>
   <si>
@@ -170,18 +131,12 @@
     <t>HEAL</t>
   </si>
   <si>
-    <t>HRTA</t>
-  </si>
-  <si>
     <t>HRUM</t>
   </si>
   <si>
     <t>ICBP</t>
   </si>
   <si>
-    <t>IMPC</t>
-  </si>
-  <si>
     <t>INCO</t>
   </si>
   <si>
@@ -191,12 +146,6 @@
     <t>INDY</t>
   </si>
   <si>
-    <t>INET</t>
-  </si>
-  <si>
-    <t>INKP</t>
-  </si>
-  <si>
     <t>ISAT</t>
   </si>
   <si>
@@ -206,18 +155,9 @@
     <t>JPFA</t>
   </si>
   <si>
-    <t>JSMR</t>
-  </si>
-  <si>
-    <t>KIJA</t>
-  </si>
-  <si>
     <t>KLBF</t>
   </si>
   <si>
-    <t>KPIG</t>
-  </si>
-  <si>
     <t>MAPA</t>
   </si>
   <si>
@@ -239,63 +179,27 @@
     <t>MYOR</t>
   </si>
   <si>
-    <t>NCKL</t>
-  </si>
-  <si>
-    <t>PANI</t>
-  </si>
-  <si>
     <t>PGAS</t>
   </si>
   <si>
-    <t>PGEO</t>
-  </si>
-  <si>
-    <t>PNLF</t>
-  </si>
-  <si>
-    <t>PSAB</t>
-  </si>
-  <si>
     <t>PTBA</t>
   </si>
   <si>
-    <t>PTRO</t>
-  </si>
-  <si>
     <t>PWON</t>
   </si>
   <si>
-    <t>RAJA</t>
-  </si>
-  <si>
-    <t>RATU</t>
-  </si>
-  <si>
     <t>SCMA</t>
   </si>
   <si>
-    <t>SGER</t>
-  </si>
-  <si>
     <t>SMGR</t>
   </si>
   <si>
-    <t>SMIL</t>
-  </si>
-  <si>
     <t>SMRA</t>
   </si>
   <si>
-    <t>SSIA</t>
-  </si>
-  <si>
     <t>TAPG</t>
   </si>
   <si>
-    <t>TINS</t>
-  </si>
-  <si>
     <t>TLKM</t>
   </si>
   <si>
@@ -314,44 +218,182 @@
     <t>UNVR</t>
   </si>
   <si>
-    <t>WIFI</t>
-  </si>
-  <si>
-    <t>WIRG</t>
-  </si>
-  <si>
-    <t>BFIN</t>
-  </si>
-  <si>
-    <t>BIPI</t>
-  </si>
-  <si>
-    <t>BNBR</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>EMAS</t>
-  </si>
-  <si>
     <t>GGRM</t>
   </si>
   <si>
     <t>LSIP</t>
   </si>
   <si>
-    <t>MINA</t>
-  </si>
-  <si>
-    <t>RMKE</t>
+    <t>BDMN</t>
+  </si>
+  <si>
+    <t>BNGA</t>
+  </si>
+  <si>
+    <t>PNBN</t>
+  </si>
+  <si>
+    <t>MEGA</t>
+  </si>
+  <si>
+    <t>TBIG</t>
+  </si>
+  <si>
+    <t>BELI</t>
+  </si>
+  <si>
+    <t>LPPF</t>
+  </si>
+  <si>
+    <t>HMSP</t>
+  </si>
+  <si>
+    <t>AUTO</t>
+  </si>
+  <si>
+    <t>DRMA</t>
+  </si>
+  <si>
+    <t>SILO</t>
+  </si>
+  <si>
+    <t>INTP</t>
+  </si>
+  <si>
+    <t>PTPP</t>
+  </si>
+  <si>
+    <t>ADHI</t>
+  </si>
+  <si>
+    <t>WIKA</t>
+  </si>
+  <si>
+    <t>AALI</t>
+  </si>
+  <si>
+    <t>BIRD</t>
+  </si>
+  <si>
+    <t>SMDR</t>
+  </si>
+  <si>
+    <t>ASSA</t>
+  </si>
+  <si>
+    <t>MBNI</t>
+  </si>
+  <si>
+    <t>BNLI</t>
+  </si>
+  <si>
+    <t>NISP</t>
+  </si>
+  <si>
+    <t>BBHI</t>
+  </si>
+  <si>
+    <t>MAYB</t>
+  </si>
+  <si>
+    <t>BJBR</t>
+  </si>
+  <si>
+    <t>BJTM</t>
+  </si>
+  <si>
+    <t>DOID</t>
+  </si>
+  <si>
+    <t>MBSS</t>
+  </si>
+  <si>
+    <t>APLN</t>
+  </si>
+  <si>
+    <t>ASRI</t>
+  </si>
+  <si>
+    <t>MDLN</t>
+  </si>
+  <si>
+    <t>MNCN</t>
+  </si>
+  <si>
+    <t>BMTR</t>
+  </si>
+  <si>
+    <t>LINK</t>
+  </si>
+  <si>
+    <t>MTEL</t>
+  </si>
+  <si>
+    <t>CENT</t>
+  </si>
+  <si>
+    <t>CPRO</t>
+  </si>
+  <si>
+    <t>MAIN</t>
+  </si>
+  <si>
+    <t>SSMS</t>
+  </si>
+  <si>
+    <t>SIMP</t>
+  </si>
+  <si>
+    <t>TBLA</t>
+  </si>
+  <si>
+    <t>STTP</t>
+  </si>
+  <si>
+    <t>ULTJ</t>
+  </si>
+  <si>
+    <t>ROTIB</t>
+  </si>
+  <si>
+    <t>SIDO</t>
+  </si>
+  <si>
+    <t>TSPC</t>
+  </si>
+  <si>
+    <t>KAEF</t>
+  </si>
+  <si>
+    <t>INAF</t>
+  </si>
+  <si>
+    <t>RALS</t>
+  </si>
+  <si>
+    <t>MPMX</t>
+  </si>
+  <si>
+    <t>SMSM</t>
+  </si>
+  <si>
+    <t>GJTL</t>
+  </si>
+  <si>
+    <t>IMAS</t>
+  </si>
+  <si>
+    <t>HEXA</t>
+  </si>
+  <si>
+    <t>MCOL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,12 +435,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -414,7 +450,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -450,6 +486,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -459,21 +508,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -758,7 +811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
@@ -768,928 +821,1048 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B2" s="5">
+      <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="6">
         <v>2</v>
       </c>
-      <c r="D2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="5">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="6">
         <v>3</v>
       </c>
-      <c r="D3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="5">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="6">
         <v>4</v>
       </c>
-      <c r="D4"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="5">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="D5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="5">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="6">
         <v>6</v>
       </c>
-      <c r="D6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="5">
-        <v>6</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="6">
         <v>7</v>
       </c>
-      <c r="D7"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="5">
-        <v>7</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B9" s="6">
         <v>8</v>
       </c>
-      <c r="D8"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="5">
-        <v>8</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4"/>
+      <c r="B10" s="6">
         <v>9</v>
       </c>
-      <c r="D9"/>
-    </row>
-    <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="5">
-        <v>9</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>10</v>
+      <c r="C10" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="D10"/>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="6">
         <v>10</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>11</v>
+      <c r="C11" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="D11"/>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="5">
+      <c r="B12" s="6">
         <v>11</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="6">
         <v>12</v>
       </c>
-      <c r="D12"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="5">
-        <v>12</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="6">
         <v>13</v>
       </c>
-      <c r="D13"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="5">
-        <v>13</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="6">
         <v>14</v>
       </c>
-      <c r="D14"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="5">
-        <v>14</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B16" s="6">
         <v>15</v>
       </c>
-      <c r="D15"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="5">
-        <v>15</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="6">
         <v>16</v>
       </c>
-      <c r="D16"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="5">
+      <c r="C17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="6">
+        <v>17</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="6">
+        <v>18</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="6">
+        <v>19</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="6">
+        <v>20</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="6">
+        <v>21</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="6">
+        <v>22</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" s="6">
+        <v>23</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="6">
+        <v>24</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="6">
+        <v>25</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B27" s="6">
+        <v>26</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B18" s="5">
-        <v>17</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B19" s="5">
-        <v>18</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" s="5">
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B28" s="6">
+        <v>27</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B29" s="6">
+        <v>28</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B30" s="6">
+        <v>29</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B31" s="6">
+        <v>30</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B32" s="6">
+        <v>31</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B33" s="6">
+        <v>32</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B34" s="6">
+        <v>33</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B35" s="6">
+        <v>34</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B36" s="6">
+        <v>35</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B37" s="6">
+        <v>36</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B38" s="6">
+        <v>37</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B39" s="6">
+        <v>38</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B40" s="6">
+        <v>39</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B41" s="6">
+        <v>40</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="5">
+      <c r="D41"/>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B42" s="6">
+        <v>41</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B22" s="5">
-        <v>21</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D22"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B23" s="5">
-        <v>22</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23"/>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B24" s="5">
-        <v>23</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="5">
-        <v>24</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" s="5">
-        <v>25</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26"/>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B27" s="5">
-        <v>26</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27"/>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B28" s="5">
-        <v>27</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28"/>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B29" s="5">
-        <v>28</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29"/>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B30" s="5">
-        <v>29</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30"/>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B31" s="5">
-        <v>30</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31"/>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B32" s="5">
-        <v>31</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D32"/>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="5">
-        <v>32</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D33"/>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B34" s="5">
-        <v>33</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34"/>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B35" s="5">
-        <v>34</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D35"/>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B36" s="5">
-        <v>35</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36"/>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B37" s="5">
-        <v>36</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D37"/>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B38" s="5">
+      <c r="D42"/>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B43" s="6">
+        <v>42</v>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38"/>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B39" s="5">
+      <c r="D43"/>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B44" s="6">
+        <v>43</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44"/>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B45" s="6">
+        <v>44</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45"/>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B46" s="6">
+        <v>45</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B47" s="6">
+        <v>46</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47"/>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B48" s="6">
+        <v>47</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B49" s="6">
+        <v>48</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B50" s="6">
+        <v>49</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B51" s="6">
+        <v>50</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B52" s="6">
+        <v>51</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B53" s="6">
+        <v>52</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B54" s="6">
+        <v>53</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54"/>
+    </row>
+    <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="4"/>
+      <c r="B55" s="6">
+        <v>54</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39"/>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B40" s="5">
-        <v>39</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D40"/>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B41" s="5">
-        <v>40</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41"/>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B42" s="5">
-        <v>41</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42"/>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B43" s="5">
-        <v>42</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43"/>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B44" s="5">
-        <v>43</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D44"/>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B45" s="5">
-        <v>44</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45"/>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B46" s="5">
-        <v>45</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D46"/>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B47" s="5">
-        <v>46</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D47"/>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B48" s="5">
-        <v>47</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D48"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B49" s="5">
-        <v>48</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D49"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B50" s="5">
-        <v>49</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D50"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B51" s="5">
-        <v>50</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D51"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B52" s="5">
-        <v>51</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D52"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B53" s="5">
-        <v>52</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D53"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B54" s="5">
-        <v>53</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D54"/>
-    </row>
-    <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="6"/>
-      <c r="B55" s="5">
-        <v>54</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="D55"/>
       <c r="G55" s="1"/>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="6"/>
-      <c r="B56" s="5">
+      <c r="A56" s="4"/>
+      <c r="B56" s="6">
         <v>55</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>50</v>
+      <c r="C56" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="D56"/>
       <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B57" s="5">
+      <c r="B57" s="6">
         <v>56</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B58" s="6">
+        <v>57</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D58"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B59" s="6">
+        <v>58</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D59"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B60" s="6">
+        <v>59</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B61" s="6">
+        <v>60</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B62" s="6">
+        <v>61</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B63" s="6">
+        <v>62</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D63"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B64" s="6">
+        <v>63</v>
+      </c>
+      <c r="C64" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D57"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B58" s="5">
-        <v>57</v>
-      </c>
-      <c r="C58" s="4" t="s">
+      <c r="D64"/>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B65" s="6">
+        <v>64</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D65"/>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B66" s="6">
+        <v>65</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D66"/>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B67" s="6">
+        <v>66</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D67"/>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B68" s="6">
+        <v>67</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D68"/>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B69" s="6">
+        <v>68</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D69"/>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B70" s="6">
+        <v>69</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70"/>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B71" s="6">
+        <v>70</v>
+      </c>
+      <c r="C71" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D58"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B59" s="5">
-        <v>58</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D59"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B60" s="5">
-        <v>59</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D60"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B61" s="5">
-        <v>60</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D61"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B62" s="5">
-        <v>61</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B63" s="5">
-        <v>62</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D63"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B64" s="5">
+      <c r="D71"/>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B72" s="6">
+        <v>71</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D72"/>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B73" s="6">
+        <v>72</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D73"/>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B74" s="6">
+        <v>73</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D74"/>
+    </row>
+    <row r="75" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B75" s="6">
+        <v>74</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D75"/>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B76" s="6">
+        <v>75</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D76"/>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B77" s="6">
+        <v>76</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D77"/>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B78" s="6">
+        <v>77</v>
+      </c>
+      <c r="C78" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D64"/>
-    </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B65" s="5">
-        <v>64</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D65"/>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B66" s="5">
-        <v>65</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D66"/>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B67" s="5">
-        <v>66</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D67"/>
-    </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B68" s="5">
-        <v>67</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D68"/>
-    </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B69" s="5">
-        <v>68</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D69"/>
-    </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B70" s="5">
-        <v>69</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D70"/>
-    </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B71" s="5">
-        <v>70</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D71"/>
-    </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B72" s="5">
-        <v>71</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D72"/>
-    </row>
-    <row r="73" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B73" s="5">
-        <v>72</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D73"/>
-    </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B74" s="5">
-        <v>73</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D74"/>
-    </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B75" s="5">
-        <v>74</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D75"/>
-    </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B76" s="5">
-        <v>75</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D76"/>
-    </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B77" s="5">
-        <v>76</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D77"/>
-    </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B78" s="5">
-        <v>77</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="D78"/>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B79" s="5">
+      <c r="B79" s="6">
         <v>78</v>
       </c>
-      <c r="C79" s="4" t="s">
-        <v>71</v>
+      <c r="C79" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="D79"/>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B80" s="5">
+      <c r="B80" s="6">
         <v>79</v>
       </c>
-      <c r="C80" s="4" t="s">
-        <v>72</v>
+      <c r="C80" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="D80"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B81" s="5">
+      <c r="B81" s="6">
         <v>80</v>
       </c>
-      <c r="C81" s="4" t="s">
-        <v>73</v>
+      <c r="C81" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="D81"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B82" s="5">
+      <c r="B82" s="6">
         <v>81</v>
       </c>
-      <c r="C82" s="4" t="s">
-        <v>74</v>
+      <c r="C82" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="D82"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B83" s="5">
+      <c r="B83" s="6">
         <v>82</v>
       </c>
-      <c r="C83" s="4" t="s">
-        <v>75</v>
+      <c r="C83" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="D83"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B84" s="5">
+      <c r="B84" s="6">
         <v>83</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>76</v>
+      <c r="C84" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="D84"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B85" s="5">
+      <c r="B85" s="6">
         <v>84</v>
       </c>
-      <c r="C85" s="4" t="s">
-        <v>101</v>
+      <c r="C85" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D85"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B86" s="5">
+      <c r="B86" s="6">
         <v>85</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>77</v>
+      <c r="C86" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="D86"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B87" s="5">
+      <c r="B87" s="6">
         <v>86</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>78</v>
+      <c r="C87" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="D87"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B88" s="5">
+      <c r="B88" s="6">
         <v>87</v>
       </c>
-      <c r="C88" s="4" t="s">
-        <v>79</v>
+      <c r="C88" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="D88"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B89" s="5">
+      <c r="B89" s="6">
         <v>88</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>80</v>
+      <c r="C89" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="D89"/>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="6"/>
-      <c r="B90" s="5">
+      <c r="A90" s="4"/>
+      <c r="B90" s="6">
         <v>89</v>
       </c>
-      <c r="C90" s="4" t="s">
-        <v>81</v>
+      <c r="C90" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="D90"/>
       <c r="G90" s="1"/>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="6"/>
-      <c r="B91" s="5">
+      <c r="A91" s="4"/>
+      <c r="B91" s="6">
         <v>90</v>
       </c>
-      <c r="C91" s="4" t="s">
-        <v>82</v>
+      <c r="C91" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="D91"/>
       <c r="G91" s="1"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B92" s="5">
+      <c r="B92" s="6">
         <v>91</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>83</v>
+      <c r="C92" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="D92"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B93" s="5">
+      <c r="B93" s="6">
         <v>92</v>
       </c>
-      <c r="C93" s="4" t="s">
-        <v>84</v>
+      <c r="C93" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="D93"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B94" s="5">
+      <c r="B94" s="6">
         <v>93</v>
       </c>
-      <c r="C94" s="4" t="s">
-        <v>85</v>
+      <c r="C94" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="D94"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B95" s="5">
+      <c r="B95" s="6">
         <v>94</v>
       </c>
-      <c r="C95" s="4" t="s">
-        <v>86</v>
+      <c r="C95" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="D95"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B96" s="5">
+      <c r="B96" s="6">
         <v>95</v>
       </c>
-      <c r="C96" s="4" t="s">
-        <v>87</v>
+      <c r="C96" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="D96"/>
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B97" s="5">
+      <c r="B97" s="6">
         <v>96</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>88</v>
+      <c r="C97" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="D97"/>
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B98" s="5">
+      <c r="B98" s="6">
         <v>97</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>89</v>
+      <c r="C98" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="D98"/>
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B99" s="5">
+      <c r="B99" s="6">
         <v>98</v>
       </c>
-      <c r="C99" s="4" t="s">
-        <v>90</v>
+      <c r="C99" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="D99"/>
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B100" s="5">
+      <c r="B100" s="6">
         <v>99</v>
       </c>
-      <c r="C100" s="4" t="s">
-        <v>91</v>
+      <c r="C100" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="D100"/>
     </row>
     <row r="101" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B101" s="5">
+      <c r="B101" s="6">
         <v>100</v>
       </c>
-      <c r="C101" s="4" t="s">
-        <v>92</v>
+      <c r="C101" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="D101"/>
     </row>
+    <row r="102" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B102" s="6">
+        <v>101</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B103" s="6">
+        <v>102</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B104" s="6">
+        <v>103</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B105" s="6">
+        <v>104</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B106" s="6">
+        <v>105</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B107" s="6">
+        <v>106</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B108" s="6">
+        <v>107</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B109" s="6">
+        <v>108</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B110" s="6">
+        <v>109</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B111" s="6">
+        <v>110</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B112" s="6">
+        <v>111</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B113" s="6">
+        <v>112</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B114" s="6">
+        <v>113</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B115" s="6">
+        <v>114</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B116" s="6">
+        <v>115</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:C101">
-    <cfRule type="expression" dxfId="0" priority="4">
+  <conditionalFormatting sqref="B2:C101 B102:B116">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>#REF!="Baru"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1702,16 +1875,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9cac375f-a6f3-411d-b129-f80e7fc560be">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="bf2d2d51-5782-4bef-9c3c-f70a66af06ee" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1981,28 +2150,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9cac375f-a6f3-411d-b129-f80e7fc560be">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="bf2d2d51-5782-4bef-9c3c-f70a66af06ee" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D872A14D-EAA8-4825-B4A4-68AB47517660}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11CCCE34-F6F6-4AAB-89F0-4C072546B45F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bf2d2d51-5782-4bef-9c3c-f70a66af06ee"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="9cac375f-a6f3-411d-b129-f80e7fc560be"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2028,9 +2191,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11CCCE34-F6F6-4AAB-89F0-4C072546B45F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D872A14D-EAA8-4825-B4A4-68AB47517660}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bf2d2d51-5782-4bef-9c3c-f70a66af06ee"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="9cac375f-a6f3-411d-b129-f80e7fc560be"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
